--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.76</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>320533344</v>
+        <v>240143949</v>
       </c>
       <c r="E2" t="n">
-        <v>2.04</v>
+        <v>-2.31</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -493,22 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.44</v>
+        <v>27.5</v>
       </c>
       <c r="D3" t="n">
-        <v>178857691</v>
+        <v>172669949</v>
       </c>
       <c r="E3" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-3.31</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -524,22 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>81.75</v>
+        <v>80.05</v>
       </c>
       <c r="D4" t="n">
-        <v>55906440</v>
+        <v>21973674</v>
       </c>
       <c r="E4" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-2.08</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -555,72 +547,72 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>166.7</v>
+        <v>167.6</v>
       </c>
       <c r="D5" t="n">
-        <v>30851316</v>
+        <v>17178832</v>
       </c>
       <c r="E5" t="n">
-        <v>1.96</v>
+        <v>0.54</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>442.8</v>
+        <v>84.5</v>
       </c>
       <c r="D6" t="n">
-        <v>24025286</v>
+        <v>13878355</v>
       </c>
       <c r="E6" t="n">
-        <v>2.26</v>
+        <v>-1.92</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>86.15000000000001</v>
+        <v>438.4</v>
       </c>
       <c r="D7" t="n">
-        <v>20988366</v>
+        <v>10443687</v>
       </c>
       <c r="E7" t="n">
-        <v>0.53</v>
+        <v>-0.99</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.529999999999999</v>
+        <v>26.92</v>
       </c>
       <c r="D2" t="n">
-        <v>240143949</v>
+        <v>169793507</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.31</v>
+        <v>-2.11</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.5</v>
+        <v>9.56</v>
       </c>
       <c r="D3" t="n">
-        <v>172669949</v>
+        <v>161530808</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.31</v>
+        <v>0.26</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -520,99 +520,99 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>80.05</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>21973674</v>
+        <v>22082644</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>167.6</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>17178832</v>
+        <v>16815586</v>
       </c>
       <c r="E5" t="n">
-        <v>0.54</v>
+        <v>-0.77</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>84.5</v>
+        <v>435.4</v>
       </c>
       <c r="D6" t="n">
-        <v>13878355</v>
+        <v>10414838</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.92</v>
+        <v>-0.68</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>438.4</v>
+        <v>164.9</v>
       </c>
       <c r="D7" t="n">
-        <v>10443687</v>
+        <v>7225458</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.99</v>
+        <v>-1.61</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26.92</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>169793507</v>
+        <v>191325722</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.11</v>
+        <v>0.52</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.56</v>
+        <v>26.38</v>
       </c>
       <c r="D3" t="n">
-        <v>161530808</v>
+        <v>120388099</v>
       </c>
       <c r="E3" t="n">
-        <v>0.26</v>
+        <v>-2.01</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>80.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="D4" t="n">
-        <v>22082644</v>
+        <v>31845013</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6899999999999999</v>
+        <v>-3.47</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>83.84999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="D5" t="n">
-        <v>16815586</v>
+        <v>27607650</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.77</v>
+        <v>-2.44</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>435.4</v>
+        <v>434</v>
       </c>
       <c r="D6" t="n">
-        <v>10414838</v>
+        <v>17647957</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.68</v>
+        <v>-0.32</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>164.9</v>
+        <v>166</v>
       </c>
       <c r="D7" t="n">
-        <v>7225458</v>
+        <v>6284877</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.61</v>
+        <v>0.67</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.609999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="D2" t="n">
-        <v>191325722</v>
+        <v>247840515</v>
       </c>
       <c r="E2" t="n">
-        <v>0.52</v>
+        <v>1.61</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.38</v>
+        <v>25.92</v>
       </c>
       <c r="D3" t="n">
-        <v>120388099</v>
+        <v>148749413</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.01</v>
+        <v>-1.74</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>77.8</v>
+        <v>74.75</v>
       </c>
       <c r="D4" t="n">
-        <v>31845013</v>
+        <v>47472774</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.47</v>
+        <v>-3.92</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>81.8</v>
+        <v>79.55</v>
       </c>
       <c r="D5" t="n">
-        <v>27607650</v>
+        <v>26257539</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.44</v>
+        <v>-2.75</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>434</v>
+        <v>425.6</v>
       </c>
       <c r="D6" t="n">
-        <v>17647957</v>
+        <v>22333265</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.32</v>
+        <v>-1.94</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>166</v>
+        <v>164.7</v>
       </c>
       <c r="D7" t="n">
-        <v>6284877</v>
+        <v>6182867</v>
       </c>
       <c r="E7" t="n">
-        <v>0.67</v>
+        <v>-0.78</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.77</v>
+        <v>9.75</v>
       </c>
       <c r="D2" t="n">
-        <v>247840515</v>
+        <v>255017158</v>
       </c>
       <c r="E2" t="n">
-        <v>1.61</v>
+        <v>-0.15</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25.92</v>
+        <v>26.36</v>
       </c>
       <c r="D3" t="n">
-        <v>148749413</v>
+        <v>113534043</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.74</v>
+        <v>1.7</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>74.75</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>47472774</v>
+        <v>25982180</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.92</v>
+        <v>0.47</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>79.55</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>26257539</v>
+        <v>21297940</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.75</v>
+        <v>0.38</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>425.6</v>
+        <v>428.4</v>
       </c>
       <c r="D6" t="n">
-        <v>22333265</v>
+        <v>15628479</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.94</v>
+        <v>0.66</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>164.7</v>
+        <v>163.3</v>
       </c>
       <c r="D7" t="n">
-        <v>6182867</v>
+        <v>9766166</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.78</v>
+        <v>-0.85</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,7 +469,7 @@
         <v>9.75</v>
       </c>
       <c r="D2" t="n">
-        <v>255017158</v>
+        <v>255012158</v>
       </c>
       <c r="E2" t="n">
         <v>-0.15</v>
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
         <v>26.36</v>
       </c>
       <c r="D3" t="n">
-        <v>113534043</v>
+        <v>113533443</v>
       </c>
       <c r="E3" t="n">
         <v>1.7</v>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>25982180</v>
+        <v>25980880</v>
       </c>
       <c r="E4" t="n">
         <v>0.47</v>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>79.84999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>21297940</v>
+        <v>21297640</v>
       </c>
       <c r="E5" t="n">
         <v>0.38</v>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         <v>428.4</v>
       </c>
       <c r="D6" t="n">
-        <v>15628479</v>
+        <v>15628379</v>
       </c>
       <c r="E6" t="n">
         <v>0.66</v>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         <v>163.3</v>
       </c>
       <c r="D7" t="n">
-        <v>9766166</v>
+        <v>9758966</v>
       </c>
       <c r="E7" t="n">
         <v>-0.85</v>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,19 +465,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>9.75</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>255012158</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.15</v>
-      </c>
+        <v>275738018</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -492,73 +488,61 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>26.36</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>113533443</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.7</v>
-      </c>
+        <v>110192077</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>75.09999999999999</v>
-      </c>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>25980880</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.47</v>
-      </c>
+        <v>19795626</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新能源</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>79.84999999999999</v>
-      </c>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>21297640</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.38</v>
-      </c>
+        <v>17248151</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -573,19 +557,15 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>428.4</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>15628379</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.66</v>
-      </c>
+        <v>11364785</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -600,19 +580,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>163.3</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>9758966</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.85</v>
-      </c>
+        <v>6723991</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,15 +465,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>9.609999999999999</v>
+      </c>
       <c r="D2" t="n">
-        <v>275738018</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>159210874</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-2.83</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
@@ -488,38 +492,46 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>26.5</v>
+      </c>
       <c r="D3" t="n">
-        <v>110192077</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>77301911</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-2.43</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>新能源</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>438.8</v>
+      </c>
       <c r="D4" t="n">
-        <v>19795626</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>21791117</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.9</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
@@ -534,61 +546,73 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>74.75</v>
+      </c>
       <c r="D5" t="n">
-        <v>17248151</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>14870839</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.4</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>159.6</v>
+      </c>
       <c r="D6" t="n">
-        <v>11364785</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>14662244</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-3.21</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>銀行</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>79.05</v>
+      </c>
       <c r="D7" t="n">
-        <v>6723991</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>12861300</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.43</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.609999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>159210874</v>
+        <v>122943726</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.83</v>
+        <v>0.26</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.5</v>
+        <v>26.18</v>
       </c>
       <c r="D3" t="n">
-        <v>77301911</v>
+        <v>74217545</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.43</v>
+        <v>-1.21</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,25 +520,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>438.8</v>
+        <v>74.45</v>
       </c>
       <c r="D4" t="n">
-        <v>21791117</v>
+        <v>16747622</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9</v>
+        <v>-0.4</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -547,72 +547,72 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74.75</v>
+        <v>433.4</v>
       </c>
       <c r="D5" t="n">
-        <v>14870839</v>
+        <v>12686515</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4</v>
+        <v>-1.23</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>159.6</v>
+        <v>79.2</v>
       </c>
       <c r="D6" t="n">
-        <v>14662244</v>
+        <v>9959680</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.21</v>
+        <v>0.19</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>79.05</v>
+        <v>160.9</v>
       </c>
       <c r="D7" t="n">
-        <v>12861300</v>
+        <v>6193653</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.43</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.640000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="D2" t="n">
-        <v>122943726</v>
+        <v>159332847</v>
       </c>
       <c r="E2" t="n">
-        <v>0.26</v>
+        <v>0.42</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.18</v>
+        <v>26.14</v>
       </c>
       <c r="D3" t="n">
-        <v>74217545</v>
+        <v>89307650</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.21</v>
+        <v>-0.15</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -520,72 +520,72 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>74.45</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>16747622</v>
+        <v>27404755</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4</v>
+        <v>-2.08</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>433.4</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>12686515</v>
+        <v>16984343</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.23</v>
+        <v>2.46</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>79.2</v>
+        <v>426</v>
       </c>
       <c r="D6" t="n">
-        <v>9959680</v>
+        <v>16185247</v>
       </c>
       <c r="E6" t="n">
-        <v>0.19</v>
+        <v>-1.71</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>160.9</v>
+        <v>159.8</v>
       </c>
       <c r="D7" t="n">
-        <v>6193653</v>
+        <v>8155068</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.68</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.68</v>
+        <v>9.59</v>
       </c>
       <c r="D2" t="n">
-        <v>159332847</v>
+        <v>266413782</v>
       </c>
       <c r="E2" t="n">
-        <v>0.42</v>
+        <v>-0.88</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.14</v>
+        <v>26.4</v>
       </c>
       <c r="D3" t="n">
-        <v>89307650</v>
+        <v>109848697</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.15</v>
+        <v>0.99</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -520,72 +520,72 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>72.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="D4" t="n">
-        <v>27404755</v>
+        <v>34129761</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.08</v>
+        <v>0.41</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>81.15000000000001</v>
+        <v>419</v>
       </c>
       <c r="D5" t="n">
-        <v>16984343</v>
+        <v>28796138</v>
       </c>
       <c r="E5" t="n">
-        <v>2.46</v>
+        <v>-1.64</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>426</v>
+        <v>81.5</v>
       </c>
       <c r="D6" t="n">
-        <v>16185247</v>
+        <v>22056501</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.71</v>
+        <v>0.43</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>159.8</v>
+        <v>161.6</v>
       </c>
       <c r="D7" t="n">
-        <v>8155068</v>
+        <v>12240089</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.68</v>
+        <v>1.13</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,61 +457,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>銀行</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>9.59</v>
-      </c>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>266413782</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.88</v>
-      </c>
+        <v>137700204</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>26.4</v>
-      </c>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>109848697</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.99</v>
-      </c>
+        <v>110209098</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,26 +511,22 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>73.2</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>34129761</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.41</v>
-      </c>
+        <v>19669433</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -546,19 +534,15 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>419</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>28796138</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-1.64</v>
-      </c>
+        <v>18568730</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -573,19 +557,15 @@
           <t>新能源</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>81.5</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>22056501</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.43</v>
-      </c>
+        <v>17650057</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -600,19 +580,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>161.6</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>12240089</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.13</v>
-      </c>
+        <v>5789115</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,46 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>9.74</v>
+      </c>
       <c r="D2" t="n">
-        <v>137700204</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>178900621</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.1</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>銀行</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>27.2</v>
+      </c>
       <c r="D3" t="n">
-        <v>110209098</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>127962106</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.38</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -511,15 +519,23 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>451.6</v>
+      </c>
       <c r="D4" t="n">
-        <v>19669433</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+        <v>70725438</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -534,15 +550,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>73.2</v>
+      </c>
       <c r="D5" t="n">
-        <v>18568730</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>22995061</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1.08</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -557,15 +577,19 @@
           <t>新能源</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>81.34999999999999</v>
+      </c>
       <c r="D6" t="n">
-        <v>17650057</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>16294565</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.18</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -580,15 +604,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>159.3</v>
+      </c>
       <c r="D7" t="n">
-        <v>5789115</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>9746155</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.36</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.74</v>
+        <v>9.66</v>
       </c>
       <c r="D2" t="n">
-        <v>178900621</v>
+        <v>155626055</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1</v>
+        <v>-0.87</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.2</v>
+        <v>26.18</v>
       </c>
       <c r="D3" t="n">
-        <v>127962106</v>
+        <v>126020027</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.38</v>
+        <v>-3.75</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -520,22 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>451.6</v>
+        <v>441</v>
       </c>
       <c r="D4" t="n">
-        <v>70725438</v>
+        <v>22310493</v>
       </c>
       <c r="E4" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-2.35</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -551,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>73.2</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>22995061</v>
+        <v>15826218</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.08</v>
+        <v>-0.48</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -578,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>81.34999999999999</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>16294565</v>
+        <v>10608954</v>
       </c>
       <c r="E6" t="n">
-        <v>0.18</v>
+        <v>-1.23</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -605,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>159.3</v>
+        <v>159.5</v>
       </c>
       <c r="D7" t="n">
-        <v>9746155</v>
+        <v>10289232</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.36</v>
+        <v>0.13</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.66</v>
+        <v>9.68</v>
       </c>
       <c r="D2" t="n">
-        <v>155626055</v>
+        <v>118811174</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.87</v>
+        <v>0.21</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.18</v>
+        <v>26.58</v>
       </c>
       <c r="D3" t="n">
-        <v>126020027</v>
+        <v>82395640</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.75</v>
+        <v>1.53</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,25 +520,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>441</v>
+        <v>72.25</v>
       </c>
       <c r="D4" t="n">
-        <v>22310493</v>
+        <v>17526084</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.35</v>
+        <v>-0.82</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>72.84999999999999</v>
+        <v>438.4</v>
       </c>
       <c r="D5" t="n">
-        <v>15826218</v>
+        <v>14278044</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.48</v>
+        <v>-0.59</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>80.34999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="D6" t="n">
-        <v>10608954</v>
+        <v>13390769</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.23</v>
+        <v>-1.06</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>159.5</v>
+        <v>156.9</v>
       </c>
       <c r="D7" t="n">
-        <v>10289232</v>
+        <v>10702028</v>
       </c>
       <c r="E7" t="n">
-        <v>0.13</v>
+        <v>-1.63</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.68</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>118811174</v>
+        <v>109459957</v>
       </c>
       <c r="E2" t="n">
-        <v>0.21</v>
+        <v>-1.5</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.58</v>
+        <v>25.9</v>
       </c>
       <c r="D3" t="n">
-        <v>82395640</v>
+        <v>78361085</v>
       </c>
       <c r="E3" t="n">
-        <v>1.53</v>
+        <v>-2.56</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -520,72 +520,72 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>72.25</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>17526084</v>
+        <v>17491240</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.82</v>
+        <v>-0.83</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>438.4</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>14278044</v>
+        <v>15461313</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.59</v>
+        <v>-1.76</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>79.5</v>
+        <v>436.6</v>
       </c>
       <c r="D6" t="n">
-        <v>13390769</v>
+        <v>9114446</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.06</v>
+        <v>-0.41</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>156.9</v>
+        <v>157.6</v>
       </c>
       <c r="D7" t="n">
-        <v>10702028</v>
+        <v>6590612</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.63</v>
+        <v>0.45</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,7 +469,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>109459957</v>
+        <v>109449957</v>
       </c>
       <c r="E2" t="n">
         <v>-1.5</v>
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
         <v>25.9</v>
       </c>
       <c r="D3" t="n">
-        <v>78361085</v>
+        <v>78353485</v>
       </c>
       <c r="E3" t="n">
         <v>-2.56</v>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>78.09999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>15461313</v>
+        <v>15449813</v>
       </c>
       <c r="E5" t="n">
         <v>-1.76</v>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         <v>436.6</v>
       </c>
       <c r="D6" t="n">
-        <v>9114446</v>
+        <v>9113746</v>
       </c>
       <c r="E6" t="n">
         <v>-0.41</v>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         <v>157.6</v>
       </c>
       <c r="D7" t="n">
-        <v>6590612</v>
+        <v>6560612</v>
       </c>
       <c r="E7" t="n">
         <v>0.45</v>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,19 +465,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>9.529999999999999</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>109449957</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-1.5</v>
-      </c>
+        <v>172750357</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -492,19 +488,15 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>25.9</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>78353485</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-2.56</v>
-      </c>
+        <v>110319422</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -519,73 +511,61 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>71.65000000000001</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>17491240</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.83</v>
-      </c>
+        <v>16902950</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新能源</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>78.09999999999999</v>
-      </c>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>15449813</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-1.76</v>
-      </c>
+        <v>15335650</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>436.6</v>
-      </c>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>9113746</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-0.41</v>
-      </c>
+        <v>14741662</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -600,19 +580,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>157.6</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>6560612</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.45</v>
-      </c>
+        <v>12829024</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -467,13 +467,13 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>172750357</v>
+        <v>263172891</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -490,13 +490,13 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>110319422</v>
+        <v>146238749</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -513,59 +513,59 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>16902950</v>
+        <v>33623155</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>15335650</v>
+        <v>28707971</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>14741662</v>
+        <v>18016336</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -582,13 +582,13 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>12829024</v>
+        <v>10739154</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -467,13 +467,13 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>263172891</v>
+        <v>232983384</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -490,13 +490,13 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>146238749</v>
+        <v>120223400</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -513,59 +513,59 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>33623155</v>
+        <v>31984827</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>28707971</v>
+        <v>22637603</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>18016336</v>
+        <v>18982984</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -582,13 +582,13 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>10739154</v>
+        <v>7997912</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,15 +465,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>9.82</v>
+      </c>
       <c r="D2" t="n">
-        <v>232983384</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>232919384</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.34</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -488,15 +492,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>25.24</v>
+      </c>
       <c r="D3" t="n">
-        <v>120223400</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>120214000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.16</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -511,15 +519,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>71.7</v>
+      </c>
       <c r="D4" t="n">
-        <v>31984827</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>31983827</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.77</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -534,15 +546,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>431</v>
+      </c>
       <c r="D5" t="n">
-        <v>22637603</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>22634903</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.23</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -557,15 +573,19 @@
           <t>新能源</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>75.59999999999999</v>
+      </c>
       <c r="D6" t="n">
-        <v>18982984</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>18982584</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.2</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -580,15 +600,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>158</v>
+      </c>
       <c r="D7" t="n">
-        <v>7997912</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>7997112</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.63</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,19 +465,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>9.82</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>232919384</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1.34</v>
-      </c>
+        <v>172060384</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
@@ -492,53 +488,45 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>25.24</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>120214000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.16</v>
-      </c>
+        <v>129404051</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>71.7</v>
-      </c>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>31983827</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.77</v>
-      </c>
+        <v>24969574</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -546,73 +534,61 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>431</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>22634903</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.23</v>
-      </c>
+        <v>22488555</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>75.59999999999999</v>
-      </c>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>18982584</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-0.2</v>
-      </c>
+        <v>19108745</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>銀行</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>158</v>
-      </c>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>7997112</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.63</v>
-      </c>
+        <v>15539618</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,15 +465,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>9.56</v>
+      </c>
       <c r="D2" t="n">
-        <v>172060384</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>171972384</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-2.7</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -488,15 +492,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>24.24</v>
+      </c>
       <c r="D3" t="n">
-        <v>129404051</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>129403051</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-3.96</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -511,15 +519,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>149.5</v>
+      </c>
       <c r="D4" t="n">
-        <v>24969574</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>24964374</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-5.38</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -534,15 +546,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>70.2</v>
+      </c>
       <c r="D5" t="n">
-        <v>22488555</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>22485255</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-2.09</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -557,15 +573,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>421.2</v>
+      </c>
       <c r="D6" t="n">
-        <v>19108745</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>19108045</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-2.27</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -580,15 +600,19 @@
           <t>新能源</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>73.90000000000001</v>
+      </c>
       <c r="D7" t="n">
-        <v>15539618</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>15537318</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-2.25</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,162 +457,162 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.56</v>
+        <v>23.88</v>
       </c>
       <c r="D2" t="n">
-        <v>171972384</v>
+        <v>88394509</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.7</v>
+        <v>-1.49</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24.24</v>
+        <v>9.51</v>
       </c>
       <c r="D3" t="n">
-        <v>129403051</v>
+        <v>70339180</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.96</v>
+        <v>-0.47</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>149.5</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>24964374</v>
+        <v>16338919</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.38</v>
+        <v>0.64</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>70.2</v>
+        <v>149.9</v>
       </c>
       <c r="D5" t="n">
-        <v>22485255</v>
+        <v>11889096</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.09</v>
+        <v>0.27</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>421.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>19108045</v>
+        <v>9860715</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.27</v>
+        <v>0.27</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>73.90000000000001</v>
+        <v>423</v>
       </c>
       <c r="D7" t="n">
-        <v>15537318</v>
+        <v>8709438</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.25</v>
+        <v>0.43</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,162 +457,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>23.88</v>
-      </c>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>88394509</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-1.49</v>
-      </c>
+        <v>98690629</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>銀行</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>9.51</v>
-      </c>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>70339180</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-0.47</v>
-      </c>
+        <v>81203405</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>70.65000000000001</v>
-      </c>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>16338919</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.64</v>
-      </c>
+        <v>10051007</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>銀行</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>149.9</v>
-      </c>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>11889096</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.27</v>
-      </c>
+        <v>10030081</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>74.09999999999999</v>
-      </c>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>9860715</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.27</v>
-      </c>
+        <v>9900789</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>423</v>
-      </c>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>8709438</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.43</v>
-      </c>
+        <v>8140224</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -467,13 +467,13 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>98690629</v>
+        <v>63054733</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -490,43 +490,43 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>81203405</v>
+        <v>46116080</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>10051007</v>
+        <v>12441640</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -536,59 +536,59 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>10030081</v>
+        <v>11286030</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>9900789</v>
+        <v>6298957</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>8140224</v>
+        <v>6125452</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -467,13 +467,13 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>63054733</v>
+        <v>224165410</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -490,43 +490,43 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>46116080</v>
+        <v>97457849</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>12441640</v>
+        <v>32302844</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -536,36 +536,36 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>11286030</v>
+        <v>30206975</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>6298957</v>
+        <v>22588514</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -582,13 +582,13 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>6125452</v>
+        <v>18847625</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,69 +457,69 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>224165410</v>
+        <v>255626451</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>97457849</v>
+        <v>170033285</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>32302844</v>
+        <v>23935883</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -536,59 +536,59 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>30206975</v>
+        <v>20420700</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>22588514</v>
+        <v>20033846</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>18847625</v>
+        <v>15671487</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,15 +465,23 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>25.96</v>
+      </c>
       <c r="D2" t="n">
-        <v>255626451</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+        <v>255608451</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -488,15 +496,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>9.73</v>
+      </c>
       <c r="D3" t="n">
-        <v>170033285</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>172126285</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.72</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -511,15 +523,23 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>71.5</v>
+      </c>
       <c r="D4" t="n">
-        <v>23935883</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+        <v>23926883</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -534,15 +554,23 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>424.8</v>
+      </c>
       <c r="D5" t="n">
-        <v>20420700</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+        <v>20422500</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -557,15 +585,23 @@
           <t>新能源</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>75.59999999999999</v>
+      </c>
       <c r="D6" t="n">
-        <v>20033846</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+        <v>20054046</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -580,15 +616,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>145.2</v>
+      </c>
       <c r="D7" t="n">
-        <v>15671487</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>15711887</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.82</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,23 +465,15 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>25.96</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>255608451</v>
-      </c>
-      <c r="E2" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>182808010</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -496,50 +488,38 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>9.73</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>172126285</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.72</v>
-      </c>
+        <v>149150984</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>71.5</v>
-      </c>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>23926883</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>24461551</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -554,54 +534,38 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>424.8</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>20422500</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>14011838</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>75.59999999999999</v>
-      </c>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>20054046</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>13773062</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -616,19 +580,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>145.2</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>15711887</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.82</v>
-      </c>
+        <v>9526825</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,46 +457,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>182808010</v>
+        <v>168953993</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>149150984</v>
+        <v>154848800</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -513,20 +513,20 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>24461551</v>
+        <v>21338036</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -536,59 +536,59 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>14011838</v>
+        <v>18242862</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>13773062</v>
+        <v>12775121</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>9526825</v>
+        <v>12729135</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,76 +457,96 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>銀行</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>26.38</v>
+      </c>
       <c r="D2" t="n">
-        <v>168953993</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+        <v>277521609</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>9.85</v>
+      </c>
       <c r="D3" t="n">
-        <v>154848800</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>187557436</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.05</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>新能源</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>77.09999999999999</v>
+      </c>
       <c r="D4" t="n">
-        <v>21338036</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+        <v>65472806</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -534,61 +554,73 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>423.4</v>
+      </c>
       <c r="D5" t="n">
-        <v>18242862</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>19933648</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.42</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>銀行</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>72.84999999999999</v>
+      </c>
       <c r="D6" t="n">
-        <v>12775121</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>15055021</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.55</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>148</v>
+      </c>
       <c r="D7" t="n">
-        <v>12729135</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>7389913</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.79</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,22 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26.38</v>
+        <v>27.08</v>
       </c>
       <c r="D2" t="n">
-        <v>277521609</v>
+        <v>266495588</v>
       </c>
       <c r="E2" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>2.65</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -497,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.85</v>
+        <v>9.98</v>
       </c>
       <c r="D3" t="n">
-        <v>187557436</v>
+        <v>226410981</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.05</v>
+        <v>1.22</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -524,22 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>77.09999999999999</v>
+        <v>75.45</v>
       </c>
       <c r="D4" t="n">
-        <v>65472806</v>
+        <v>33700990</v>
       </c>
       <c r="E4" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-2.14</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -555,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>423.4</v>
+        <v>417.8</v>
       </c>
       <c r="D5" t="n">
-        <v>19933648</v>
+        <v>20660817</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.42</v>
+        <v>-1.32</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -582,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>72.84999999999999</v>
+        <v>72.95</v>
       </c>
       <c r="D6" t="n">
-        <v>15055021</v>
+        <v>16039825</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.55</v>
+        <v>0.14</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -609,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>148</v>
+        <v>147.9</v>
       </c>
       <c r="D7" t="n">
-        <v>7389913</v>
+        <v>10134643</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.79</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.08</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>266495588</v>
+        <v>182667483</v>
       </c>
       <c r="E2" t="n">
-        <v>2.65</v>
+        <v>-1.1</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.98</v>
+        <v>26.66</v>
       </c>
       <c r="D3" t="n">
-        <v>226410981</v>
+        <v>154063468</v>
       </c>
       <c r="E3" t="n">
-        <v>1.22</v>
+        <v>-1.55</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>75.45</v>
+        <v>75.7</v>
       </c>
       <c r="D4" t="n">
-        <v>33700990</v>
+        <v>22668265</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.14</v>
+        <v>0.33</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -550,15 +550,15 @@
         <v>417.8</v>
       </c>
       <c r="D5" t="n">
-        <v>20660817</v>
+        <v>18749869</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.32</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>72.95</v>
+        <v>73.75</v>
       </c>
       <c r="D6" t="n">
-        <v>16039825</v>
+        <v>12782058</v>
       </c>
       <c r="E6" t="n">
-        <v>0.14</v>
+        <v>1.1</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>147.9</v>
+        <v>149.7</v>
       </c>
       <c r="D7" t="n">
-        <v>10134643</v>
+        <v>12156298</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,7 +469,7 @@
         <v>9.859999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>182667483</v>
+        <v>183102483</v>
       </c>
       <c r="E2" t="n">
         <v>-1.1</v>
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
         <v>26.66</v>
       </c>
       <c r="D3" t="n">
-        <v>154063468</v>
+        <v>154063268</v>
       </c>
       <c r="E3" t="n">
         <v>-1.55</v>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
         <v>75.7</v>
       </c>
       <c r="D4" t="n">
-        <v>22668265</v>
+        <v>22655665</v>
       </c>
       <c r="E4" t="n">
         <v>0.33</v>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>417.8</v>
       </c>
       <c r="D5" t="n">
-        <v>18749869</v>
+        <v>18752869</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         <v>73.75</v>
       </c>
       <c r="D6" t="n">
-        <v>12782058</v>
+        <v>12817758</v>
       </c>
       <c r="E6" t="n">
         <v>1.1</v>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         <v>149.7</v>
       </c>
       <c r="D7" t="n">
-        <v>12156298</v>
+        <v>12339898</v>
       </c>
       <c r="E7" t="n">
         <v>1.22</v>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.859999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>183102483</v>
+        <v>159435945</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.1</v>
+        <v>-0.86</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.66</v>
+        <v>27.06</v>
       </c>
       <c r="D3" t="n">
-        <v>154063268</v>
+        <v>106056819</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.55</v>
+        <v>1.5</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>75.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>22655665</v>
+        <v>23683952</v>
       </c>
       <c r="E4" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -547,72 +547,72 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>417.8</v>
+        <v>410.4</v>
       </c>
       <c r="D5" t="n">
-        <v>18752869</v>
+        <v>22820913</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-1.77</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>73.75</v>
+        <v>144.7</v>
       </c>
       <c r="D6" t="n">
-        <v>12817758</v>
+        <v>13990598</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1</v>
+        <v>-3.34</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>149.7</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>12339898</v>
+        <v>13626766</v>
       </c>
       <c r="E7" t="n">
-        <v>1.22</v>
+        <v>-0.14</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,15 +469,15 @@
         <v>9.779999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>159435945</v>
+        <v>146759276</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.86</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.06</v>
+        <v>26.8</v>
       </c>
       <c r="D3" t="n">
-        <v>106056819</v>
+        <v>144467851</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5</v>
+        <v>-0.96</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,25 +520,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>76.09999999999999</v>
+        <v>393.8</v>
       </c>
       <c r="D4" t="n">
-        <v>23683952</v>
+        <v>37783935</v>
       </c>
       <c r="E4" t="n">
-        <v>0.53</v>
+        <v>-4.04</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -547,72 +547,72 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>410.4</v>
+        <v>74.7</v>
       </c>
       <c r="D5" t="n">
-        <v>22820913</v>
+        <v>20550985</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.77</v>
+        <v>-1.84</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>144.7</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>13990598</v>
+        <v>19481840</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.34</v>
+        <v>-3.39</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>73.65000000000001</v>
+        <v>145.8</v>
       </c>
       <c r="D7" t="n">
-        <v>13626766</v>
+        <v>5470795</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.14</v>
+        <v>0.76</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.779999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>146759276</v>
+        <v>265447170</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.8</v>
+        <v>25.8</v>
       </c>
       <c r="D3" t="n">
-        <v>144467851</v>
+        <v>149479760</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.96</v>
+        <v>-3.73</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>393.8</v>
+        <v>382.4</v>
       </c>
       <c r="D4" t="n">
-        <v>37783935</v>
+        <v>60746647</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.04</v>
+        <v>-2.89</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74.7</v>
+        <v>71.3</v>
       </c>
       <c r="D5" t="n">
-        <v>20550985</v>
+        <v>37843088</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.84</v>
+        <v>-4.55</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>71.15000000000001</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>19481840</v>
+        <v>35128666</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.39</v>
+        <v>-5.27</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>145.8</v>
+        <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>5470795</v>
+        <v>10622221</v>
       </c>
       <c r="E7" t="n">
-        <v>0.76</v>
+        <v>-1.23</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.720000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="D2" t="n">
-        <v>265447170</v>
+        <v>412306503</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.61</v>
+        <v>0.46</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -493,52 +493,60 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25.8</v>
+        <v>26.8</v>
       </c>
       <c r="D3" t="n">
-        <v>149479760</v>
+        <v>216291102</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.73</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>3.88</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>382.4</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>60746647</v>
+        <v>51639425</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.89</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>6.23</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -547,45 +555,45 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>71.3</v>
+        <v>386</v>
       </c>
       <c r="D5" t="n">
-        <v>37843088</v>
+        <v>33142473</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.55</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67.40000000000001</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>35128666</v>
+        <v>30566200</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.27</v>
+        <v>0.49</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -601,18 +609,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>144</v>
+        <v>142.5</v>
       </c>
       <c r="D7" t="n">
-        <v>10622221</v>
+        <v>11995864</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.23</v>
+        <v>-1.04</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,7 +469,7 @@
         <v>9.77</v>
       </c>
       <c r="D2" t="n">
-        <v>412306503</v>
+        <v>412299503</v>
       </c>
       <c r="E2" t="n">
         <v>0.46</v>
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
         <v>26.8</v>
       </c>
       <c r="D3" t="n">
-        <v>216291102</v>
+        <v>216285102</v>
       </c>
       <c r="E3" t="n">
         <v>3.88</v>
@@ -508,7 +508,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
         <v>71.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>51639425</v>
+        <v>51810625</v>
       </c>
       <c r="E4" t="n">
         <v>6.23</v>
@@ -539,7 +539,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
         <v>386</v>
       </c>
       <c r="D5" t="n">
-        <v>33142473</v>
+        <v>33161473</v>
       </c>
       <c r="E5" t="n">
         <v>0.9399999999999999</v>
@@ -566,7 +566,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         <v>71.65000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>30566200</v>
+        <v>30564900</v>
       </c>
       <c r="E6" t="n">
         <v>0.49</v>
@@ -593,7 +593,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
         <v>142.5</v>
       </c>
       <c r="D7" t="n">
-        <v>11995864</v>
+        <v>12090264</v>
       </c>
       <c r="E7" t="n">
         <v>-1.04</v>
@@ -620,7 +620,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,19 +465,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>9.77</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>412299503</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.46</v>
-      </c>
+        <v>198560002</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -492,88 +488,68 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>26.8</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>216285102</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>93023145</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>新能源</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>71.59999999999999</v>
-      </c>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>51810625</v>
-      </c>
-      <c r="E4" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>37179856</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>386</v>
-      </c>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>33161473</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+        <v>18430441</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -581,19 +557,15 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>71.65000000000001</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>30564900</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.49</v>
-      </c>
+        <v>16943609</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -608,19 +580,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>142.5</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>12090264</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-1.04</v>
-      </c>
+        <v>11151564</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,15 +465,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
       <c r="D2" t="n">
-        <v>198560002</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>264849822</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -488,61 +492,73 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>25.66</v>
+      </c>
       <c r="D3" t="n">
-        <v>93023145</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>138340888</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-4.61</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>134.3</v>
+      </c>
       <c r="D4" t="n">
-        <v>37179856</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>36513272</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-5.56</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新能源</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>71.84999999999999</v>
+      </c>
       <c r="D5" t="n">
-        <v>18430441</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>21809697</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-2.97</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -557,38 +573,46 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>385.2</v>
+      </c>
       <c r="D6" t="n">
-        <v>16943609</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>16238414</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.31</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>銀行</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>70.05</v>
+      </c>
       <c r="D7" t="n">
-        <v>11151564</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>15914527</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.06</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,19 +465,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>10</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>264849822</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
+        <v>179382541</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -492,73 +488,61 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>25.66</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>138340888</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-4.61</v>
-      </c>
+        <v>76649974</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>銀行</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>134.3</v>
-      </c>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>36513272</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-5.56</v>
-      </c>
+        <v>23325345</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>71.84999999999999</v>
-      </c>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>21809697</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-2.97</v>
-      </c>
+        <v>18651098</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -573,19 +557,15 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>385.2</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>16238414</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-0.31</v>
-      </c>
+        <v>13705006</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -600,19 +580,15 @@
           <t>新能源</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>70.05</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>15914527</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-1.06</v>
-      </c>
+        <v>13585186</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -467,13 +467,13 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>179382541</v>
+        <v>316260623</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -490,13 +490,13 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>76649974</v>
+        <v>88051677</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -513,36 +513,36 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>23325345</v>
+        <v>27175118</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>18651098</v>
+        <v>21268279</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -559,36 +559,36 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>13705006</v>
+        <v>20994465</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>13585186</v>
+        <v>9668716</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -467,13 +467,13 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>316260623</v>
+        <v>281495562</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -490,59 +490,59 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>88051677</v>
+        <v>207860564</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>27175118</v>
+        <v>36602423</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>21268279</v>
+        <v>36190642</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -559,13 +559,13 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>20994465</v>
+        <v>22275554</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -582,13 +582,13 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>9668716</v>
+        <v>10700902</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
